--- a/files/fe63f44fcca5/ipji-template.xlsx
+++ b/files/fe63f44fcca5/ipji-template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -106,8 +106,39 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF2B3445"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF14181F"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF2B3445"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <i val="1"/>
+      <color rgb="FF5A6172"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -154,8 +185,56 @@
         <fgColor rgb="FF8B9A7E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B2A4E"/>
+        <bgColor rgb="FF1B2A4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3E63"/>
+        <bgColor rgb="FF2F3E63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE4F0"/>
+        <bgColor rgb="FFDDE4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFCFE"/>
+        <bgColor rgb="FFFBFCFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B3A5C"/>
+        <bgColor rgb="FF2B3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A5D86"/>
+        <bgColor rgb="FF4A5D86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF1F7"/>
+        <bgColor rgb="FFEEF1F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor rgb="FFF6F8FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -255,11 +334,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D3E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9D3E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9D3E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -304,6 +446,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,6 +853,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B2A4E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -680,266 +866,266 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" s="9">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>아파트 입지 분석</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="16" t="n"/>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="22" t="n"/>
     </row>
     <row r="2" ht="20.1" customHeight="1" s="9">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>입지 4대 요소 심층 분석 · 결영이네 원팀 프로젝트</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="16" t="n"/>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="22" t="n"/>
     </row>
     <row r="3" ht="24.95" customHeight="1" s="9">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>단지명</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="16" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="22" t="n"/>
     </row>
     <row r="4" ht="24.95" customHeight="1" s="9">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="16" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="22" t="n"/>
     </row>
     <row r="5" ht="24.95" customHeight="1" s="9">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>연식</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="16" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="22" t="n"/>
     </row>
     <row r="6" ht="24.95" customHeight="1" s="9">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>용적률, 건폐율</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="16" t="n"/>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="22" t="n"/>
     </row>
     <row r="7" ht="24.95" customHeight="1" s="9">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>세대수</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="16" t="n"/>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="22" t="n"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" s="9">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>주차대수</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="16" t="n"/>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="22" t="n"/>
     </row>
     <row r="9" ht="24.95" customHeight="1" s="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>평형</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="16" t="n"/>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="22" t="n"/>
     </row>
     <row r="10" ht="24.95" customHeight="1" s="9">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>매매가</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="16" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="22" t="n"/>
     </row>
     <row r="11" ht="24.95" customHeight="1" s="9">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>전세가</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="16" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="22" t="n"/>
     </row>
     <row r="12" ht="8.1" customHeight="1" s="9"/>
     <row r="13" ht="24" customHeight="1" s="9">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>세부 항목</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>분석 내용</t>
         </is>
       </c>
     </row>
     <row r="14" ht="51.95" customHeight="1" s="9">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>일자리·교통</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>일자리</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="29" t="n"/>
     </row>
     <row r="15" ht="51.95" customHeight="1" s="9">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>역세권</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="32" t="n"/>
     </row>
     <row r="16" ht="51.95" customHeight="1" s="9">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>도로·버스</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="29" t="n"/>
     </row>
     <row r="17" ht="51.95" customHeight="1" s="9">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>학군</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>초품아</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="29" t="n"/>
     </row>
     <row r="18" ht="51.95" customHeight="1" s="9">
-      <c r="A18" s="13" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>중학교</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="32" t="n"/>
     </row>
     <row r="19" ht="39.95" customHeight="1" s="9">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>고등학교</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="29" t="n"/>
     </row>
     <row r="20" ht="51.95" customHeight="1" s="9">
-      <c r="A20" s="14" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>학원가</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="32" t="n"/>
     </row>
     <row r="21" ht="51.95" customHeight="1" s="9">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>상권 및 생활환경</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>상권·쇼핑</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
+      <c r="C21" s="29" t="n"/>
     </row>
     <row r="22" ht="39.95" customHeight="1" s="9">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>의료</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="32" t="n"/>
     </row>
     <row r="23" ht="39.95" customHeight="1" s="9">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>편의시설</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="29" t="n"/>
     </row>
     <row r="24" ht="51.95" customHeight="1" s="9">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>문화·여가</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="32" t="n"/>
     </row>
     <row r="25" ht="51.95" customHeight="1" s="9">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">프리미엄 </t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>개발호재</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
+      <c r="C25" s="29" t="n"/>
     </row>
     <row r="26" ht="39.95" customHeight="1" s="9">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="32" t="n"/>
     </row>
     <row r="27" ht="78" customHeight="1" s="9">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
+      <c r="B27" s="35" t="n"/>
+      <c r="C27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>둘이서 함께하는 부의 첫걸음 · 원팀 프로젝트</t>
         </is>
@@ -949,6 +1135,7 @@
   <mergeCells count="17">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A14:A16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -960,7 +1147,6 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A14:A16"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A2:C2"/>
@@ -973,6 +1159,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B2A4E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -985,325 +1172,325 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" s="9">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>아파트 입지 분석</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="16" t="n"/>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="22" t="n"/>
     </row>
     <row r="2" ht="20.1" customHeight="1" s="9">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>입지 4대 요소 심층 분석 · 결영이네 원팀 프로젝트</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="16" t="n"/>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="22" t="n"/>
     </row>
     <row r="3" ht="24.95" customHeight="1" s="9">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>단지명</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>DMC센트럴자이</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n"/>
+      <c r="C3" s="22" t="n"/>
     </row>
     <row r="4" ht="24.95" customHeight="1" s="9">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>서울시 은평구 증산동 258~261</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n"/>
+      <c r="C4" s="22" t="n"/>
     </row>
     <row r="5" ht="24.95" customHeight="1" s="9">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>연식</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">2023년 1월 · 4년차 </t>
         </is>
       </c>
-      <c r="C5" s="16" t="n"/>
+      <c r="C5" s="22" t="n"/>
     </row>
     <row r="6" ht="24.95" customHeight="1" s="9">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>용적률, 건폐율</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>용적률 250.93% , 건폐율 21.43%</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
+      <c r="C6" s="22" t="n"/>
     </row>
     <row r="7" ht="24.95" customHeight="1" s="9">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>세대수</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">총 1,256세대(임대 164세대) </t>
         </is>
       </c>
-      <c r="C7" s="16" t="n"/>
+      <c r="C7" s="22" t="n"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" s="9">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>주차대수</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>총 1,541대 (세대당 1.22대)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n"/>
+      <c r="C8" s="22" t="n"/>
     </row>
     <row r="9" ht="24.95" customHeight="1" s="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>평형</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>전용 59㎡ / 74㎡ / 84㎡</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n"/>
+      <c r="C9" s="22" t="n"/>
     </row>
     <row r="10" ht="24.95" customHeight="1" s="9">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>매매가</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>15/16/17.5</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n"/>
+      <c r="C10" s="22" t="n"/>
     </row>
     <row r="11" ht="24.95" customHeight="1" s="9">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>전세가</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>7/7.9/8.8</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n"/>
+      <c r="C11" s="22" t="n"/>
     </row>
     <row r="12" ht="8.1" customHeight="1" s="9"/>
     <row r="13" ht="24" customHeight="1" s="9">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>세부 항목</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>분석 내용</t>
         </is>
       </c>
     </row>
     <row r="14" ht="51.95" customHeight="1" s="9">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>일자리·교통</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>일자리</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>DMC 업무지구 도보 출퇴근 가능,  마곡 20분, 광화문·여의도 약 30분, 강남 1시간 이내</t>
         </is>
       </c>
     </row>
     <row r="15" ht="51.95" customHeight="1" s="9">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>역세권</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>디지털미디어시티역 (6호선·공항철도·경의중앙선) 도보 5분</t>
         </is>
       </c>
     </row>
     <row r="16" ht="51.95" customHeight="1" s="9">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>도로·버스</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>버스 도보 5분 이내, 내부순환로(성산IC)·강변북로·월드컵대교 접근성 용이</t>
         </is>
       </c>
     </row>
     <row r="17" ht="51.95" customHeight="1" s="9">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>학군</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>초품아</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>증산초 초품아  도보 5분 이내 (동마다 차이 있음)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="51.95" customHeight="1" s="9">
-      <c r="A18" s="13" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>중학교</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">증산중 (도보권). 충암·연서·숭실·상신중 등 서부2학교군 배정 </t>
         </is>
       </c>
     </row>
     <row r="19" ht="39.95" customHeight="1" s="9">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>고등학교</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>가재울고(도보권), 숭실고·충암고 등 진학</t>
         </is>
       </c>
     </row>
     <row r="20" ht="51.95" customHeight="1" s="9">
-      <c r="A20" s="14" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>학원가</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>가재울뉴타운 학원가, 대흥동 학원가 셔틀버스</t>
         </is>
       </c>
     </row>
     <row r="21" ht="51.95" customHeight="1" s="9">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>상권 및 생활환경</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>상권·쇼핑</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>이마트, 홈플러스  도보권, DMC롯데몰 예정, 유명프랜차이즈 다수(파바,올리브영,스타벅스 등)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39.95" customHeight="1" s="9">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>의료</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>신촌세브란스, 은평성모병원 종합병원 접근성 양호</t>
         </is>
       </c>
     </row>
     <row r="23" ht="39.95" customHeight="1" s="9">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>편의시설</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>주민센터, 은평구청, 보건소 접근성 양호</t>
         </is>
       </c>
     </row>
     <row r="24" ht="51.95" customHeight="1" s="9">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>문화·여가</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>증산도서관, 상암월드컵경기장, 영화관 등 인근 문화시설 접근 양호</t>
         </is>
       </c>
     </row>
     <row r="25" ht="51.95" customHeight="1" s="9">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">프리미엄 </t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>개발호재</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>교통 - 서부선 경전철, 강북횡단선 개발 예정
 인프라 - 롯데몰, 삼표부지 개발 호재</t>
@@ -1311,29 +1498,29 @@
       </c>
     </row>
     <row r="26" ht="39.95" customHeight="1" s="9">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">불광천 수변산책로, 증산체육공원, 상암 월드컵공원(하늘·노을·평화공원) </t>
         </is>
       </c>
     </row>
     <row r="27" ht="78" customHeight="1" s="9">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
+      <c r="B27" s="35" t="n"/>
+      <c r="C27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>둘이서 함께하는 부의 첫걸음 · 원팀 프로젝트</t>
         </is>
@@ -1343,7 +1530,6 @@
   <mergeCells count="17">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A14:A16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -1352,12 +1538,13 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
